--- a/lessons/wall/excels/remarks_leo_star.xlsx
+++ b/lessons/wall/excels/remarks_leo_star.xlsx
@@ -179,7 +179,7 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-1px (10:08:30.398), -gray (10:08:30.508), +400px* (10:23:08.698), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +0 (00:00:00), +5px (00:00:00), +grey (00:00:00)</t>
+        <t>-1px (10:08:30.398), -gray (10:08:30.508) ~0.75, +400px* (10:23:08.698), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +0 (00:00:00), +5px (00:00:00), +grey (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -204,7 +204,7 @@
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:01:30.574), -1px (10:08:30.398), -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647), -chess (10:19:31.372), -- (10:19:31.521), -board (10:19:32.570), -{ (10:19:36.298), -} (10:19:37.045), -width (10:19:39.292), -: (10:19:39.478), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -; (10:25:53.393), +display* (10:26:45.844), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +div (00:00:00), +2px (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
+        <t>-} (10:01:30.574), -1px (10:08:30.398) ~0.67, -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647) ~0.00, -chess (10:19:31.372), -- (10:19:31.521), -board (10:19:32.570), -{ (10:19:36.298), -} (10:19:37.045), -width (10:19:39.292), -: (10:19:39.478), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -; (10:25:53.393), +display* (10:26:45.844), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002) ~1.00, -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +div (00:00:00), +2px (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -224,12 +224,12 @@
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
       <text>
-        <t>-Board (09:36:35.655), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -- (10:19:01.973), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -light (10:30:44.589), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +board (00:00:00), +My (00:00:00), +first (00:00:00), +web (00:00:00), +page (00:00:00)</t>
+        <t>-Board (09:36:35.655) ~0.80, -Chess (09:42:49.678) ~0.20, -Board (09:42:50.360) ~0.20, -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -- (10:19:01.973), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -light (10:30:44.589), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +board (00:00:00), +My (00:00:00), +first (00:00:00), +web (00:00:00), +page (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:01:30.574), -border (10:08:30.348), -1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +10px (00:00:00), +padding (00:00:00), +: (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
+        <t>-} (10:01:30.574), -border (10:08:30.348), -1px (10:08:30.398) ~0.75, +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002) ~1.00, -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +10px (00:00:00), +padding (00:00:00), +: (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -249,7 +249,7 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (09:34:25.996), -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +doctype (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +height (00:00:00), +50px (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Chess (00:00:00), +Board (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +! (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +com (00:00:00), +/ (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00)</t>
+        <t>-DOCTYPE (09:34:25.996) ~0.00, -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +doctype (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +height (00:00:00), +50px (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Chess (00:00:00), +Board (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +! (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +com (00:00:00), +/ (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
@@ -299,12 +299,12 @@
     </comment>
     <comment ref="M25" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (09:36:34.482), -Board (09:36:35.655), -&lt; (09:37:18.806), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -" (10:19:03.420), -light (10:29:10.001), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:39.899), -&lt; (10:30:41.052), -&gt; (10:30:41.102), -&lt; (10:30:41.132), -div (10:30:41.162), -class (10:30:41.222), -= (10:30:41.232), -" (10:30:41.242), -cell (10:30:41.282), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -&lt; (10:30:41.362), -/ (10:30:41.372), -div (10:30:41.402), -&gt; (10:30:41.412), -&lt; (10:30:41.432), -&lt; (10:30:41.513), -/ (10:30:41.523), -div (10:30:41.553), -&gt; (10:30:41.563), -&lt; (10:30:41.593), -div (10:30:41.623), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -cell (10:30:41.743), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -div (10:30:41.863), -&gt; (10:30:41.873), -&lt; (10:30:41.893), -div (10:30:41.923), -class (10:30:41.983), -= (10:30:41.993), -&lt; (10:30:42.169), -/ (10:30:42.179), -div (10:30:42.209), -&gt; (10:30:42.219), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.339), -= (10:30:42.349), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.639), -= (10:30:42.649), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -&lt; (10:30:44.009), -/ (10:30:44.019), -div (10:30:44.049), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +chess (00:00:00), +board (00:00:00)</t>
+        <t>-Chess (09:36:34.482) ~0.80, -Board (09:36:35.655) ~0.80, -&lt; (09:37:18.806), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -" (10:19:03.420), -light (10:29:10.001), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:39.899), -&lt; (10:30:41.052), -&gt; (10:30:41.102), -&lt; (10:30:41.132), -div (10:30:41.162), -class (10:30:41.222), -= (10:30:41.232), -" (10:30:41.242), -cell (10:30:41.282), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -&lt; (10:30:41.362), -/ (10:30:41.372), -div (10:30:41.402), -&gt; (10:30:41.412), -&lt; (10:30:41.432), -&lt; (10:30:41.513), -/ (10:30:41.523), -div (10:30:41.553), -&gt; (10:30:41.563), -&lt; (10:30:41.593), -div (10:30:41.623), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -cell (10:30:41.743), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -div (10:30:41.863), -&gt; (10:30:41.873), -&lt; (10:30:41.893), -div (10:30:41.923), -class (10:30:41.983), -= (10:30:41.993), -&lt; (10:30:42.169), -/ (10:30:42.179), -div (10:30:42.209), -&gt; (10:30:42.219), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.339), -= (10:30:42.349), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.639), -= (10:30:42.649), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -&lt; (10:30:44.009), -/ (10:30:44.019), -div (10:30:44.049), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +chess (00:00:00), +board (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-1px (10:08:30.398), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +430px (00:00:00), +red (00:00:00), +5px (00:00:00)</t>
+        <t>-1px (10:08:30.398) ~0.67, +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382) ~0.60, +430px (00:00:00), +red (00:00:00), +5px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -324,12 +324,12 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (09:35:08.944), -&gt; (09:35:10.226), -Chess (09:36:34.482), -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -Chess (09:42:49.678), -Board (09:42:50.360), -/ (09:42:50.549), -h1 (09:42:50.973), -&gt; (09:42:51.209), -&lt; (09:43:40.713), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -board (10:19:03.204), -" (10:19:03.420), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +title (00:00:00), +* (00:00:00), +I (00:00:00), +turned (00:00:00), +up (00:00:00), +late (00:00:00), +bus (00:00:00), +was (00:00:00), +able (00:00:00), +to (00:00:00), +follow (00:00:00), +along (00:00:00), +when (00:00:00), +you (00:00:00), +were (00:00:00), +talking (00:00:00), +about (00:00:00), +the (00:00:00), +allignmenot (00:00:00), +of (00:00:00), +marging (00:00:00), +, (00:00:00), +colors (00:00:00), +and (00:00:00), +pixels (00:00:00), +I (00:00:00), +not (00:00:00), +get (00:00:00), +working (00:00:00), +program (00:00:00), +but (00:00:00), +was (00:00:00), +able (00:00:00), +to (00:00:00), +gain (00:00:00), +some (00:00:00), +insight (00:00:00), +into (00:00:00), +how (00:00:00), +basic (00:00:00), +form (00:00:00), +is (00:00:00), +constructed (00:00:00), +* (00:00:00)</t>
+        <t>-&lt; (09:35:08.944), -&gt; (09:35:10.226), -Chess (09:36:34.482) ~0.00, -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -Chess (09:42:49.678), -Board (09:42:50.360), -/ (09:42:50.549), -h1 (09:42:50.973), -&gt; (09:42:51.209), -&lt; (09:43:40.713), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -board (10:19:03.204), -" (10:19:03.420), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +title (00:00:00), +* (00:00:00), +I (00:00:00), +turned (00:00:00), +up (00:00:00), +late (00:00:00), +bus (00:00:00), +was (00:00:00), +able (00:00:00), +to (00:00:00), +follow (00:00:00), +along (00:00:00), +when (00:00:00), +you (00:00:00), +were (00:00:00), +talking (00:00:00), +about (00:00:00), +the (00:00:00), +allignmenot (00:00:00), +of (00:00:00), +marging (00:00:00), +, (00:00:00), +colors (00:00:00), +and (00:00:00), +pixels (00:00:00), +I (00:00:00), +not (00:00:00), +get (00:00:00), +working (00:00:00), +program (00:00:00), +but (00:00:00), +was (00:00:00), +able (00:00:00), +to (00:00:00), +gain (00:00:00), +some (00:00:00), +insight (00:00:00), +into (00:00:00), +how (00:00:00), +basic (00:00:00), +form (00:00:00), +is (00:00:00), +constructed (00:00:00), +* (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
-        <t>-height (10:01:53.339), -50px (10:01:53.779), +400px* (10:23:08.698), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:18.655), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +hight (00:00:00), +50 (00:00:00), +px (00:00:00)</t>
+        <t>-height (10:01:53.339) ~0.83, -50px (10:01:53.779) ~0.50, +400px* (10:23:08.698), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:18.655), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +hight (00:00:00), +50 (00:00:00), +px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D36" authorId="0" shapeId="0">
@@ -384,7 +384,7 @@
     </comment>
     <comment ref="M51" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (09:34:25.996), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +doCtyPe (00:00:00)</t>
+        <t>-DOCTYPE (09:34:25.996) ~0.29, -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +doCtyPe (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O51" authorId="0" shapeId="0">
@@ -409,12 +409,12 @@
     </comment>
     <comment ref="M56" authorId="0" shapeId="0">
       <text>
-        <t>-! (09:43:41.273), -a (09:43:41.313), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-! (09:43:41.273), -a (09:43:41.313), -left (10:40:20.194) ~0.00, -- (10:40:20.358) ~0.00, -offset (10:40:21.332), -left (10:40:38.720) ~0.00, -- (10:40:38.730) ~0.00, -offset (10:40:38.790), -left (10:40:42.564) ~0.00, -- (10:40:42.574) ~0.00, -offset (10:40:42.634), -left (10:40:46.355) ~0.00, -- (10:40:46.365) ~0.00, -offset (10:40:46.425) ~0.00, +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O56" authorId="0" shapeId="0">
       <text>
-        <t>-gray (10:08:30.508), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), -425px (10:41:03.382), +440px (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +padding (00:00:00), +0px (00:00:00), +; (00:00:00), +: (00:00:00), +green (00:00:00)</t>
+        <t>-gray (10:08:30.508) ~0.40, +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), -425px (10:41:03.382) ~0.60, +440px (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +padding (00:00:00), +0px (00:00:00), +; (00:00:00), +: (00:00:00), +green (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
@@ -434,12 +434,12 @@
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
-        <t>-/ (09:35:09.192), -html (09:35:09.958), -&gt; (09:35:10.226), -&gt; (09:37:18.022), -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -&gt; (09:42:48.974), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:42:50.459), -/ (09:42:50.549), -h1 (09:42:50.973), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -div (10:13:39.615), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -" (10:19:03.420), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +table (00:00:00)</t>
+        <t>-/ (09:35:09.192), -html (09:35:09.958), -&gt; (09:35:10.226), -&gt; (09:37:18.022), -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -&gt; (09:42:48.974), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:42:50.459), -/ (09:42:50.549), -h1 (09:42:50.973), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -div (10:13:39.615), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247) ~0.00, -" (10:19:03.420), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +table (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-{ (10:01:29.863), -} (10:01:30.574), -: (10:01:53.349), -50px (10:01:53.399), -; (10:01:53.409), -: (10:01:53.729), -50px (10:01:53.779), -; (10:01:53.789), -1px (10:08:30.398), -gray (10:08:30.508), -; (10:08:30.518), -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647), -} (10:19:37.045), -width (10:19:39.292), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +2px (00:00:00), +black (00:00:00), +; (00:00:00), +- (00:00:00), +collapse (00:00:00), +: (00:00:00), +collapse (00:00:00), +400px (00:00:00), +; (00:00:00), +400px (00:00:00)</t>
+        <t>-{ (10:01:29.863), -} (10:01:30.574), -: (10:01:53.349), -50px (10:01:53.399), -; (10:01:53.409), -: (10:01:53.729), -50px (10:01:53.779), -; (10:01:53.789), -1px (10:08:30.398), -gray (10:08:30.508), -; (10:08:30.518), -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647), -} (10:19:37.045), -width (10:19:39.292), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003) ~0.40, -425px (10:41:03.382) ~0.60, -; (10:41:03.595), +2px (00:00:00), +black (00:00:00), +; (00:00:00), +- (00:00:00), +collapse (00:00:00), +: (00:00:00), +collapse (00:00:00), +400px (00:00:00), +; (00:00:00), +400px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E71" authorId="0" shapeId="0">
@@ -454,7 +454,7 @@
     </comment>
     <comment ref="M71" authorId="0" shapeId="0">
       <text>
-        <t>-" (09:43:40.793), -" (09:43:41.053), -W3Schools (09:43:41.223), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -chess (10:19:01.762), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -&lt; (10:30:40.039), -/ (10:30:40.049), -div (10:30:40.079), -&gt; (10:30:40.089), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.199), -= (10:30:40.209), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -&lt; (10:30:40.649), -/ (10:30:40.659), -div (10:30:40.689), -&gt; (10:30:40.699), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.809), -= (10:30:40.819), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -&lt; (10:30:43.089), -/ (10:30:43.099), -div (10:30:43.129), -&gt; (10:30:43.139), -&lt; (10:30:43.159), -div (10:30:43.189), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +Chess (00:00:00), +w3schools (00:00:00)</t>
+        <t>-" (09:43:40.793), -" (09:43:41.053), -W3Schools (09:43:41.223) ~0.78, -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -chess (10:19:01.762) ~0.80, -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -&lt; (10:30:40.039), -/ (10:30:40.049), -div (10:30:40.079), -&gt; (10:30:40.089), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.199), -= (10:30:40.209), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -&lt; (10:30:40.649), -/ (10:30:40.659), -div (10:30:40.689), -&gt; (10:30:40.699), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.809), -= (10:30:40.819), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -&lt; (10:30:43.089), -/ (10:30:43.099), -div (10:30:43.129), -&gt; (10:30:43.139), -&lt; (10:30:43.159), -div (10:30:43.189), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +Chess (00:00:00), +w3schools (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O71" authorId="0" shapeId="0">
@@ -484,12 +484,12 @@
     </comment>
     <comment ref="M73" authorId="0" shapeId="0">
       <text>
-        <t>-_ (09:53:33.438), -blank (09:53:34.696), -/ (09:54:45.543), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -div (10:30:31.152), -class (10:30:31.212), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +! (00:00:00), +with (00:00:00), +Inline (00:00:00), +style (00:00:00), +( (00:00:00), +Not (00:00:00), +recommended (00:00:00), +) (00:00:00), +div (00:00:00), +style (00:00:00), +height (00:00:00), +50px (00:00:00), +: (00:00:00), +width (00:00:00), +50px (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +padding (00:00:00), +5px (00:00:00), +2px (00:00:00), +solid (00:00:00), +gray (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +black (00:00:00)</t>
+        <t>-_ (09:53:33.438), -blank (09:53:34.696) ~0.80, -/ (09:54:45.543), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -div (10:30:31.152), -class (10:30:31.212), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +! (00:00:00), +with (00:00:00), +Inline (00:00:00), +style (00:00:00), +( (00:00:00), +Not (00:00:00), +recommended (00:00:00), +) (00:00:00), +div (00:00:00), +style (00:00:00), +height (00:00:00), +50px (00:00:00), +: (00:00:00), +width (00:00:00), +50px (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +padding (00:00:00), +5px (00:00:00), +2px (00:00:00), +solid (00:00:00), +gray (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +black (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O73" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:01:30.574), -1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -- (10:23:53.510), -box (10:23:53.913), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -white (10:28:26.840), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +; (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00), +2px (00:00:00), +inline (00:00:00), +block (00:00:00)</t>
+        <t>-} (10:01:30.574), -1px (10:08:30.398) ~0.75, +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319) ~1.00, -sizing (10:23:52.062), -- (10:23:53.510), -box (10:23:53.913), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -white (10:28:26.840), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +; (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00), +2px (00:00:00), +inline (00:00:00), +block (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D75" authorId="0" shapeId="0">
@@ -514,12 +514,12 @@
     </comment>
     <comment ref="M75" authorId="0" shapeId="0">
       <text>
-        <t>-Visit (09:43:41.123), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +visit (00:00:00)</t>
+        <t>-Visit (09:43:41.123) ~0.80, -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +visit (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>+display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +432px (00:00:00), +; (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00)</t>
+        <t>+display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382) ~0.60, +432px (00:00:00), +; (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -539,12 +539,12 @@
     </comment>
     <comment ref="M78" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (09:42:49.678), -Board (09:42:50.360), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -light (10:29:10.001), -div (10:30:31.152), -class (10:30:31.212), -cell (10:30:31.272), -dark (10:30:31.322), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -div (10:30:36.692), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -cell (10:30:39.293), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -&lt; (10:30:39.383), -/ (10:30:39.393), -div (10:30:39.423), -&gt; (10:30:39.433), -&lt; (10:30:39.453), -div (10:30:39.483), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -cell (10:30:39.603), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -&lt; (10:30:39.993), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -class (10:30:40.199), -= (10:30:40.209), -cell (10:30:40.213), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -&lt; (10:30:40.603), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -class (10:30:40.809), -= (10:30:40.819), -cell (10:30:40.823), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -/ (10:30:42.443), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -/ (10:30:43.053), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -div (10:30:43.189), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +chess (00:00:00), +board (00:00:00), +style (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00), +width (00:00:00), +50px (00:00:00), +visit (00:00:00), +w3schools (00:00:00)</t>
+        <t>-Chess (09:42:49.678) ~0.80, -Board (09:42:50.360) ~0.80, -Visit (09:43:41.123) ~0.80, -W3Schools (09:43:41.223) ~0.78, -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -light (10:29:10.001), -div (10:30:31.152), -class (10:30:31.212), -cell (10:30:31.272), -dark (10:30:31.322), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -div (10:30:36.692), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -cell (10:30:39.293), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -&lt; (10:30:39.383), -/ (10:30:39.393), -div (10:30:39.423), -&gt; (10:30:39.433), -&lt; (10:30:39.453), -div (10:30:39.483), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -cell (10:30:39.603), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -&lt; (10:30:39.993), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -class (10:30:40.199), -= (10:30:40.209), -cell (10:30:40.213), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -&lt; (10:30:40.603), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -class (10:30:40.809), -= (10:30:40.819), -cell (10:30:40.823), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -/ (10:30:42.443), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -/ (10:30:43.053), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -div (10:30:43.189), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +chess (00:00:00), +board (00:00:00), +style (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00), +width (00:00:00), +50px (00:00:00), +visit (00:00:00), +w3schools (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
       <text>
-        <t>-1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), -display (10:25:49.056), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +2px (00:00:00)</t>
+        <t>-1px (10:08:30.398) ~0.67, +;* (10:23:07.806), +400px* (10:23:08.698), -display (10:25:49.056), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +2px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E79" authorId="0" shapeId="0">
@@ -564,7 +564,7 @@
     </comment>
     <comment ref="O79" authorId="0" shapeId="0">
       <text>
-        <t>+background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -425px (10:41:03.382), +432px (00:00:00)</t>
+        <t>+background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -425px (10:41:03.382) ~0.60, +432px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
@@ -584,7 +584,7 @@
     </comment>
     <comment ref="M81" authorId="0" shapeId="0">
       <text>
-        <t>-W3Schools (09:43:41.223), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +W3schools (00:00:00)</t>
+        <t>-W3Schools (09:43:41.223) ~0.89, -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +W3schools (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O81" authorId="0" shapeId="0">
@@ -634,12 +634,12 @@
     </comment>
     <comment ref="M83" authorId="0" shapeId="0">
       <text>
-        <t>-Visit (09:43:41.123), -W3Schools (09:43:41.223), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +visit (00:00:00), +w3schools (00:00:00)</t>
+        <t>-Visit (09:43:41.123) ~0.80, -W3Schools (09:43:41.223) ~0.78, -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +visit (00:00:00), +w3schools (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O83" authorId="0" shapeId="0">
       <text>
-        <t>-1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +2px (00:00:00)</t>
+        <t>-1px (10:08:30.398) ~0.67, +;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +2px (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-1px (10:08:30.398), -gray (10:08:30.508), +400px* (10:23:08.698), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +0 (00:00:00), +5px (00:00:00), +grey (00:00:00)</t>
+          <t>-1px (10:08:30.398), -gray (10:08:30.508) ~0.75, +400px* (10:23:08.698), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +0 (00:00:00), +5px (00:00:00), +grey (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-} (10:01:30.574), -1px (10:08:30.398), -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647), -chess (10:19:31.372), -- (10:19:31.521), -board (10:19:32.570), -{ (10:19:36.298), -} (10:19:37.045), -width (10:19:39.292), -: (10:19:39.478), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -; (10:25:53.393), +display* (10:26:45.844), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +div (00:00:00), +2px (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
+          <t>-} (10:01:30.574), -1px (10:08:30.398) ~0.67, -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647) ~0.00, -chess (10:19:31.372), -- (10:19:31.521), -board (10:19:32.570), -{ (10:19:36.298), -} (10:19:37.045), -width (10:19:39.292), -: (10:19:39.478), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -; (10:25:53.393), +display* (10:26:45.844), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002) ~1.00, -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +div (00:00:00), +2px (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-Board (09:36:35.655), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -- (10:19:01.973), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -light (10:30:44.589), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +board (00:00:00), +My (00:00:00), +first (00:00:00), +web (00:00:00), +page (00:00:00)</t>
+          <t>-Board (09:36:35.655) ~0.80, -Chess (09:42:49.678) ~0.20, -Board (09:42:50.360) ~0.20, -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -- (10:19:01.973), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -light (10:30:44.589), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +board (00:00:00), +My (00:00:00), +first (00:00:00), +web (00:00:00), +page (00:00:00)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-} (10:01:30.574), -border (10:08:30.348), -1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +10px (00:00:00), +padding (00:00:00), +: (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
+          <t>-} (10:01:30.574), -border (10:08:30.348), -1px (10:08:30.398) ~0.75, +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002) ~1.00, -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +10px (00:00:00), +padding (00:00:00), +: (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-DOCTYPE (09:34:25.996), -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +doctype (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +height (00:00:00), +50px (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Chess (00:00:00), +Board (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +! (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +com (00:00:00), +/ (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00)</t>
+          <t>-DOCTYPE (09:34:25.996) ~0.00, -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +doctype (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +height (00:00:00), +50px (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Chess (00:00:00), +Board (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +! (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +com (00:00:00), +/ (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-Chess (09:36:34.482), -Board (09:36:35.655), -&lt; (09:37:18.806), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -" (10:19:03.420), -light (10:29:10.001), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:39.899), -&lt; (10:30:41.052), -&gt; (10:30:41.102), -&lt; (10:30:41.132), -div (10:30:41.162), -class (10:30:41.222), -= (10:30:41.232), -" (10:30:41.242), -cell (10:30:41.282), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -&lt; (10:30:41.362), -/ (10:30:41.372), -div (10:30:41.402), -&gt; (10:30:41.412), -&lt; (10:30:41.432), -&lt; (10:30:41.513), -/ (10:30:41.523), -div (10:30:41.553), -&gt; (10:30:41.563), -&lt; (10:30:41.593), -div (10:30:41.623), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -cell (10:30:41.743), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -div (10:30:41.863), -&gt; (10:30:41.873), -&lt; (10:30:41.893), -div (10:30:41.923), -class (10:30:41.983), -= (10:30:41.993), -&lt; (10:30:42.169), -/ (10:30:42.179), -div (10:30:42.209), -&gt; (10:30:42.219), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.339), -= (10:30:42.349), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.639), -= (10:30:42.649), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -&lt; (10:30:44.009), -/ (10:30:44.019), -div (10:30:44.049), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +chess (00:00:00), +board (00:00:00)</t>
+          <t>-Chess (09:36:34.482) ~0.80, -Board (09:36:35.655) ~0.80, -&lt; (09:37:18.806), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -" (10:19:03.420), -light (10:29:10.001), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:39.899), -&lt; (10:30:41.052), -&gt; (10:30:41.102), -&lt; (10:30:41.132), -div (10:30:41.162), -class (10:30:41.222), -= (10:30:41.232), -" (10:30:41.242), -cell (10:30:41.282), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -&lt; (10:30:41.362), -/ (10:30:41.372), -div (10:30:41.402), -&gt; (10:30:41.412), -&lt; (10:30:41.432), -&lt; (10:30:41.513), -/ (10:30:41.523), -div (10:30:41.553), -&gt; (10:30:41.563), -&lt; (10:30:41.593), -div (10:30:41.623), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -cell (10:30:41.743), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -div (10:30:41.863), -&gt; (10:30:41.873), -&lt; (10:30:41.893), -div (10:30:41.923), -class (10:30:41.983), -= (10:30:41.993), -&lt; (10:30:42.169), -/ (10:30:42.179), -div (10:30:42.209), -&gt; (10:30:42.219), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.339), -= (10:30:42.349), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.639), -= (10:30:42.649), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -&lt; (10:30:44.009), -/ (10:30:44.019), -div (10:30:44.049), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +chess (00:00:00), +board (00:00:00)</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-1px (10:08:30.398), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +430px (00:00:00), +red (00:00:00), +5px (00:00:00)</t>
+          <t>-1px (10:08:30.398) ~0.67, +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382) ~0.60, +430px (00:00:00), +red (00:00:00), +5px (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-&lt; (09:35:08.944), -&gt; (09:35:10.226), -Chess (09:36:34.482), -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -Chess (09:42:49.678), -Board (09:42:50.360), -/ (09:42:50.549), -h1 (09:42:50.973), -&gt; (09:42:51.209), -&lt; (09:43:40.713), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -board (10:19:03.204), -" (10:19:03.420), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +title (00:00:00), +* (00:00:00), +I (00:00:00), +turned (00:00:00), +up (00:00:00), +late (00:00:00), +bus (00:00:00), +was (00:00:00), +able (00:00:00), +to (00:00:00), +follow (00:00:00), +along (00:00:00), +when (00:00:00), +you (00:00:00), +were (00:00:00), +talking (00:00:00), +about (00:00:00), +the (00:00:00), +allignmenot (00:00:00), +of (00:00:00), +marging (00:00:00), +, (00:00:00), +colors (00:00:00), +and (00:00:00), +pixels (00:00:00), +I (00:00:00), +not (00:00:00), +get (00:00:00), +working (00:00:00), +program (00:00:00), +but (00:00:00), +was (00:00:00), +able (00:00:00), +to (00:00:00), +gain (00:00:00), +some (00:00:00), +insight (00:00:00), +into (00:00:00), +how (00:00:00), +basic (00:00:00), +form (00:00:00), +is (00:00:00), +constructed (00:00:00), +* (00:00:00)</t>
+          <t>-&lt; (09:35:08.944), -&gt; (09:35:10.226), -Chess (09:36:34.482) ~0.00, -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -Chess (09:42:49.678), -Board (09:42:50.360), -/ (09:42:50.549), -h1 (09:42:50.973), -&gt; (09:42:51.209), -&lt; (09:43:40.713), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -board (10:19:03.204), -" (10:19:03.420), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +title (00:00:00), +* (00:00:00), +I (00:00:00), +turned (00:00:00), +up (00:00:00), +late (00:00:00), +bus (00:00:00), +was (00:00:00), +able (00:00:00), +to (00:00:00), +follow (00:00:00), +along (00:00:00), +when (00:00:00), +you (00:00:00), +were (00:00:00), +talking (00:00:00), +about (00:00:00), +the (00:00:00), +allignmenot (00:00:00), +of (00:00:00), +marging (00:00:00), +, (00:00:00), +colors (00:00:00), +and (00:00:00), +pixels (00:00:00), +I (00:00:00), +not (00:00:00), +get (00:00:00), +working (00:00:00), +program (00:00:00), +but (00:00:00), +was (00:00:00), +able (00:00:00), +to (00:00:00), +gain (00:00:00), +some (00:00:00), +insight (00:00:00), +into (00:00:00), +how (00:00:00), +basic (00:00:00), +form (00:00:00), +is (00:00:00), +constructed (00:00:00), +* (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-height (10:01:53.339), -50px (10:01:53.779), +400px* (10:23:08.698), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:18.655), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +hight (00:00:00), +50 (00:00:00), +px (00:00:00)</t>
+          <t>-height (10:01:53.339) ~0.83, -50px (10:01:53.779) ~0.50, +400px* (10:23:08.698), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:18.655), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +hight (00:00:00), +50 (00:00:00), +px (00:00:00)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>-DOCTYPE (09:34:25.996), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +doCtyPe (00:00:00)</t>
+          <t>-DOCTYPE (09:34:25.996) ~0.29, -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +doCtyPe (00:00:00)</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>-! (09:43:41.273), -a (09:43:41.313), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-! (09:43:41.273), -a (09:43:41.313), -left (10:40:20.194) ~0.00, -- (10:40:20.358) ~0.00, -offset (10:40:21.332), -left (10:40:38.720) ~0.00, -- (10:40:38.730) ~0.00, -offset (10:40:38.790), -left (10:40:42.564) ~0.00, -- (10:40:42.574) ~0.00, -offset (10:40:42.634), -left (10:40:46.355) ~0.00, -- (10:40:46.365) ~0.00, -offset (10:40:46.425) ~0.00, +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-gray (10:08:30.508), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), -425px (10:41:03.382), +440px (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +padding (00:00:00), +0px (00:00:00), +; (00:00:00), +: (00:00:00), +green (00:00:00)</t>
+          <t>-gray (10:08:30.508) ~0.40, +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), -425px (10:41:03.382) ~0.60, +440px (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +padding (00:00:00), +0px (00:00:00), +; (00:00:00), +: (00:00:00), +green (00:00:00)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-/ (09:35:09.192), -html (09:35:09.958), -&gt; (09:35:10.226), -&gt; (09:37:18.022), -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -&gt; (09:42:48.974), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:42:50.459), -/ (09:42:50.549), -h1 (09:42:50.973), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -div (10:13:39.615), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -" (10:19:03.420), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +table (00:00:00)</t>
+          <t>-/ (09:35:09.192), -html (09:35:09.958), -&gt; (09:35:10.226), -&gt; (09:37:18.022), -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -&gt; (09:42:48.974), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:42:50.459), -/ (09:42:50.549), -h1 (09:42:50.973), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -div (10:13:39.615), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247) ~0.00, -" (10:19:03.420), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +table (00:00:00)</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-{ (10:01:29.863), -} (10:01:30.574), -: (10:01:53.349), -50px (10:01:53.399), -; (10:01:53.409), -: (10:01:53.729), -50px (10:01:53.779), -; (10:01:53.789), -1px (10:08:30.398), -gray (10:08:30.508), -; (10:08:30.518), -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647), -} (10:19:37.045), -width (10:19:39.292), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +2px (00:00:00), +black (00:00:00), +; (00:00:00), +- (00:00:00), +collapse (00:00:00), +: (00:00:00), +collapse (00:00:00), +400px (00:00:00), +; (00:00:00), +400px (00:00:00)</t>
+          <t>-{ (10:01:29.863), -} (10:01:30.574), -: (10:01:53.349), -50px (10:01:53.399), -; (10:01:53.409), -: (10:01:53.729), -50px (10:01:53.779), -; (10:01:53.789), -1px (10:08:30.398), -gray (10:08:30.508), -; (10:08:30.518), -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647), -} (10:19:37.045), -width (10:19:39.292), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003) ~0.40, -425px (10:41:03.382) ~0.60, -; (10:41:03.595), +2px (00:00:00), +black (00:00:00), +; (00:00:00), +- (00:00:00), +collapse (00:00:00), +: (00:00:00), +collapse (00:00:00), +400px (00:00:00), +; (00:00:00), +400px (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>-" (09:43:40.793), -" (09:43:41.053), -W3Schools (09:43:41.223), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -chess (10:19:01.762), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -&lt; (10:30:40.039), -/ (10:30:40.049), -div (10:30:40.079), -&gt; (10:30:40.089), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.199), -= (10:30:40.209), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -&lt; (10:30:40.649), -/ (10:30:40.659), -div (10:30:40.689), -&gt; (10:30:40.699), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.809), -= (10:30:40.819), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -&lt; (10:30:43.089), -/ (10:30:43.099), -div (10:30:43.129), -&gt; (10:30:43.139), -&lt; (10:30:43.159), -div (10:30:43.189), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +Chess (00:00:00), +w3schools (00:00:00)</t>
+          <t>-" (09:43:40.793), -" (09:43:41.053), -W3Schools (09:43:41.223) ~0.78, -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -chess (10:19:01.762) ~0.80, -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -&lt; (10:30:40.039), -/ (10:30:40.049), -div (10:30:40.079), -&gt; (10:30:40.089), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.199), -= (10:30:40.209), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -&lt; (10:30:40.649), -/ (10:30:40.659), -div (10:30:40.689), -&gt; (10:30:40.699), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.809), -= (10:30:40.819), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -&lt; (10:30:43.089), -/ (10:30:43.099), -div (10:30:43.129), -&gt; (10:30:43.139), -&lt; (10:30:43.159), -div (10:30:43.189), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +Chess (00:00:00), +w3schools (00:00:00)</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>-_ (09:53:33.438), -blank (09:53:34.696), -/ (09:54:45.543), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -div (10:30:31.152), -class (10:30:31.212), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +! (00:00:00), +with (00:00:00), +Inline (00:00:00), +style (00:00:00), +( (00:00:00), +Not (00:00:00), +recommended (00:00:00), +) (00:00:00), +div (00:00:00), +style (00:00:00), +height (00:00:00), +50px (00:00:00), +: (00:00:00), +width (00:00:00), +50px (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +padding (00:00:00), +5px (00:00:00), +2px (00:00:00), +solid (00:00:00), +gray (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +black (00:00:00)</t>
+          <t>-_ (09:53:33.438), -blank (09:53:34.696) ~0.80, -/ (09:54:45.543), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -div (10:30:31.152), -class (10:30:31.212), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -div (10:30:44.659), -&gt; (10:30:44.669), -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +! (00:00:00), +with (00:00:00), +Inline (00:00:00), +style (00:00:00), +( (00:00:00), +Not (00:00:00), +recommended (00:00:00), +) (00:00:00), +div (00:00:00), +style (00:00:00), +height (00:00:00), +50px (00:00:00), +: (00:00:00), +width (00:00:00), +50px (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +padding (00:00:00), +5px (00:00:00), +2px (00:00:00), +solid (00:00:00), +gray (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +black (00:00:00)</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>-} (10:01:30.574), -1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -- (10:23:53.510), -box (10:23:53.913), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -white (10:28:26.840), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +; (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00), +2px (00:00:00), +inline (00:00:00), +block (00:00:00)</t>
+          <t>-} (10:01:30.574), -1px (10:08:30.398) ~0.75, +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319) ~1.00, -sizing (10:23:52.062), -- (10:23:53.510), -box (10:23:53.913), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -white (10:28:26.840), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +; (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00), +2px (00:00:00), +inline (00:00:00), +block (00:00:00)</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>-Visit (09:43:41.123), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +visit (00:00:00)</t>
+          <t>-Visit (09:43:41.123) ~0.80, -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +visit (00:00:00)</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>+display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +432px (00:00:00), +; (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00)</t>
+          <t>+display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382) ~0.60, +432px (00:00:00), +; (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-Chess (09:42:49.678), -Board (09:42:50.360), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -light (10:29:10.001), -div (10:30:31.152), -class (10:30:31.212), -cell (10:30:31.272), -dark (10:30:31.322), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -div (10:30:36.692), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -cell (10:30:39.293), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -&lt; (10:30:39.383), -/ (10:30:39.393), -div (10:30:39.423), -&gt; (10:30:39.433), -&lt; (10:30:39.453), -div (10:30:39.483), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -cell (10:30:39.603), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -&lt; (10:30:39.993), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -class (10:30:40.199), -= (10:30:40.209), -cell (10:30:40.213), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -&lt; (10:30:40.603), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -class (10:30:40.809), -= (10:30:40.819), -cell (10:30:40.823), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -/ (10:30:42.443), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -/ (10:30:43.053), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -div (10:30:43.189), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +chess (00:00:00), +board (00:00:00), +style (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00), +width (00:00:00), +50px (00:00:00), +visit (00:00:00), +w3schools (00:00:00)</t>
+          <t>-Chess (09:42:49.678) ~0.80, -Board (09:42:50.360) ~0.80, -Visit (09:43:41.123) ~0.80, -W3Schools (09:43:41.223) ~0.78, -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -light (10:29:10.001), -div (10:30:31.152), -class (10:30:31.212), -cell (10:30:31.272), -dark (10:30:31.322), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -div (10:30:36.692), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -cell (10:30:39.293), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -&lt; (10:30:39.383), -/ (10:30:39.393), -div (10:30:39.423), -&gt; (10:30:39.433), -&lt; (10:30:39.453), -div (10:30:39.483), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -cell (10:30:39.603), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -&lt; (10:30:39.993), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -class (10:30:40.199), -= (10:30:40.209), -cell (10:30:40.213), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -&lt; (10:30:40.603), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -class (10:30:40.809), -= (10:30:40.819), -cell (10:30:40.823), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -/ (10:30:42.443), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -/ (10:30:43.053), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -div (10:30:43.189), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +chess (00:00:00), +board (00:00:00), +style (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00), +width (00:00:00), +50px (00:00:00), +visit (00:00:00), +w3schools (00:00:00)</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), -display (10:25:49.056), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +2px (00:00:00)</t>
+          <t>-1px (10:08:30.398) ~0.67, +;* (10:23:07.806), +400px* (10:23:08.698), -display (10:25:49.056), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +2px (00:00:00)</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>+background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -425px (10:41:03.382), +432px (00:00:00)</t>
+          <t>+background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -425px (10:41:03.382) ~0.60, +432px (00:00:00)</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>-W3Schools (09:43:41.223), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +W3schools (00:00:00)</t>
+          <t>-W3Schools (09:43:41.223) ~0.89, -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +W3schools (00:00:00)</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>-Visit (09:43:41.123), -W3Schools (09:43:41.223), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +visit (00:00:00), +w3schools (00:00:00)</t>
+          <t>-Visit (09:43:41.123) ~0.80, -W3Schools (09:43:41.223) ~0.78, -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), +visit (00:00:00), +w3schools (00:00:00)</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>-1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +2px (00:00:00)</t>
+          <t>-1px (10:08:30.398) ~0.67, +;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +2px (00:00:00)</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">

--- a/lessons/wall/excels/remarks_leo_star.xlsx
+++ b/lessons/wall/excels/remarks_leo_star.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,20 @@
     </font>
     <font>
       <name val="Segoe UI Emoji"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -64,12 +78,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1076,22 +1096,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1112,22 +1116,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1180,7 +1168,6 @@
           <t>+- (00:00:00), +0 (00:00:00), +5px (00:00:00), +: (00:00:00), +; (00:00:00), +background (00:00:00), +black (00:00:00), +color (00:00:00), +grey (00:00:00), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -1px (10:08:30.398), -gray (10:08:30.508), -&gt; (10:13:46.973), +400px* (10:23:08.698), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>95.40000000000001</v>
       </c>
@@ -1197,12 +1184,11 @@
           <t>-1px (10:08:30.398), -gray (10:08:30.508) ~0.75, +400px* (10:23:08.698), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +0 (00:00:00), +5px (00:00:00), +grey (00:00:00)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1250,7 +1236,6 @@
           <t>+- (00:00:00), +2px (00:00:00), +: (00:00:00), +block (00:00:00), +div (00:00:00), +inline (00:00:00), -" (09:43:41.053), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -&lt; (09:54:44.535), -div (09:54:46.214), -&gt; (09:54:46.231), -} (10:01:30.574), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.967), -&gt; (10:03:04.977), -1px (10:08:30.398), -&gt; (10:13:40.081), -. (10:16:02.523), -cell (10:16:03.341), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -chess (10:19:01.762), -- (10:19:01.973), -board (10:19:03.204), -" (10:19:03.420), -# (10:19:26.647), -chess (10:19:31.372), -- (10:19:31.521), -board (10:19:32.570), -{ (10:19:36.298), -} (10:19:37.045), -width (10:19:39.292), -: (10:19:39.478), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -; (10:25:53.393), +display* (10:26:45.844), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -cell (10:30:41.433), -" (10:30:41.439), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -div (10:30:41.909), -&gt; (10:30:41.919), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>16.5</v>
       </c>
@@ -1267,12 +1252,11 @@
           <t>-} (10:01:30.574), -1px (10:08:30.398) ~0.67, -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647) ~0.00, -chess (10:19:31.372), -- (10:19:31.521), -board (10:19:32.570), -{ (10:19:36.298), -} (10:19:37.045), -width (10:19:39.292), -: (10:19:39.478), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -; (10:25:53.393), +display* (10:26:45.844), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002) ~1.00, -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +div (00:00:00), +2px (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1289,20 +1273,6 @@
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,22 +1288,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1354,22 +1308,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1391,20 +1329,6 @@
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1420,22 +1344,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1456,22 +1364,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1493,20 +1385,6 @@
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1522,22 +1400,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1559,20 +1421,6 @@
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1588,22 +1436,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1624,22 +1456,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1660,22 +1476,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1696,22 +1496,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1764,7 +1548,6 @@
           <t>+- (00:00:00), +0 (00:00:00), +10px (00:00:00), +2px (00:00:00), +: (00:00:00), +: (00:00:00), +My (00:00:00), +block (00:00:00), +board (00:00:00), +display (00:00:00), +first (00:00:00), +font (00:00:00), +inline (00:00:00), +padding (00:00:00), +page (00:00:00), +size (00:00:00), +web (00:00:00), -Board (09:36:35.655), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -} (10:01:30.574), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -border (10:08:30.348), -1px (10:08:30.398), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -- (10:19:01.973), +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -light (10:30:44.589), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>18.6</v>
       </c>
@@ -1781,12 +1564,11 @@
           <t>-} (10:01:30.574), -border (10:08:30.348), -1px (10:08:30.398) ~0.75, +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002) ~1.00, -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +10px (00:00:00), +padding (00:00:00), +: (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1802,22 +1584,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1870,7 +1636,6 @@
           <t>+! (00:00:00), +! (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +50px (00:00:00), +50px (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Board (00:00:00), +Chess (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +a (00:00:00), +a (00:00:00), +background (00:00:00), +black (00:00:00), +body (00:00:00), +body (00:00:00), +color (00:00:00), +com (00:00:00), +com (00:00:00), +div (00:00:00), +doctype (00:00:00), +height (00:00:00), +href (00:00:00), +https (00:00:00), +style (00:00:00), +w3schools (00:00:00), +width (00:00:00), +www (00:00:00), -DOCTYPE (09:34:25.996), +400px* (10:23:08.698), -display (10:25:49.056), -flex (10:25:49.961), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>92.90000000000001</v>
       </c>
@@ -1887,12 +1652,11 @@
           <t>+400px* (10:23:08.698), -display (10:25:49.056), -flex (10:25:49.961), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1908,22 +1672,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1944,22 +1692,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2033,12 +1765,11 @@
           <t>+;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -} (10:39:26.734), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -; (10:39:32.366), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2086,7 +1817,6 @@
           <t>+430px (00:00:00), +5px (00:00:00), +board (00:00:00), +chess (00:00:00), +red (00:00:00), -Chess (09:36:34.482), -Board (09:36:35.655), -&lt; (09:37:18.806), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -1px (10:08:30.398), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -" (10:19:03.420), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -light (10:29:10.001), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:39.899), -&lt; (10:30:41.052), -&gt; (10:30:41.102), -&lt; (10:30:41.132), -div (10:30:41.162), -class (10:30:41.222), -= (10:30:41.232), -" (10:30:41.242), -cell (10:30:41.282), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -&lt; (10:30:41.362), -/ (10:30:41.372), -div (10:30:41.402), -&gt; (10:30:41.412), -&lt; (10:30:41.432), -&lt; (10:30:41.513), -/ (10:30:41.523), -div (10:30:41.553), -&gt; (10:30:41.563), -&lt; (10:30:41.593), -div (10:30:41.623), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -cell (10:30:41.743), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -div (10:30:41.863), -&gt; (10:30:41.873), -&lt; (10:30:41.893), -div (10:30:41.923), -class (10:30:41.983), -= (10:30:41.993), -&lt; (10:30:42.169), -/ (10:30:42.179), -div (10:30:42.209), -&gt; (10:30:42.219), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.339), -= (10:30:42.349), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.639), -= (10:30:42.649), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -&lt; (10:30:44.009), -/ (10:30:44.019), -div (10:30:44.049), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>82.7</v>
       </c>
@@ -2103,12 +1833,11 @@
           <t>-1px (10:08:30.398) ~0.67, +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382) ~0.60, +430px (00:00:00), +red (00:00:00), +5px (00:00:00)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2124,22 +1853,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2160,22 +1873,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2197,20 +1894,6 @@
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2226,22 +1909,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2263,20 +1930,6 @@
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2324,7 +1977,6 @@
           <t>+* (00:00:00), +* (00:00:00), +, (00:00:00), +50 (00:00:00), +I (00:00:00), +I (00:00:00), +able (00:00:00), +able (00:00:00), +about (00:00:00), +allignmenot (00:00:00), +along (00:00:00), +and (00:00:00), +basic (00:00:00), +bus (00:00:00), +but (00:00:00), +colors (00:00:00), +constructed (00:00:00), +follow (00:00:00), +form (00:00:00), +gain (00:00:00), +get (00:00:00), +hight (00:00:00), +how (00:00:00), +insight (00:00:00), +into (00:00:00), +is (00:00:00), +late (00:00:00), +marging (00:00:00), +not (00:00:00), +of (00:00:00), +pixels (00:00:00), +program (00:00:00), +px (00:00:00), +some (00:00:00), +talking (00:00:00), +the (00:00:00), +title (00:00:00), +to (00:00:00), +to (00:00:00), +turned (00:00:00), +up (00:00:00), +was (00:00:00), +was (00:00:00), +were (00:00:00), +when (00:00:00), +working (00:00:00), +you (00:00:00), -&lt; (09:35:08.944), -&gt; (09:35:10.226), -Chess (09:36:34.482), -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -Chess (09:42:49.678), -Board (09:42:50.360), -/ (09:42:50.549), -h1 (09:42:50.973), -&gt; (09:42:51.209), -&lt; (09:43:40.713), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -height (10:01:53.339), -50px (10:01:53.779), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -- (10:19:01.973), -board (10:19:03.204), -" (10:19:03.420), +400px* (10:23:08.698), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:18.655), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -; (10:28:47.044), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -2341,12 +1993,11 @@
           <t>-height (10:01:53.339) ~0.83, -50px (10:01:53.779) ~0.50, +400px* (10:23:08.698), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:18.655), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +hight (00:00:00), +50 (00:00:00), +px (00:00:00)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2362,22 +2013,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2398,22 +2033,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2434,22 +2053,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2470,22 +2073,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2511,22 +2098,11 @@
           <t>⛔</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Scr</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2542,22 +2118,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2578,22 +2138,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2614,22 +2158,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2650,22 +2178,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2718,7 +2230,6 @@
           <t>+html (00:00:00), -&lt; (09:34:24.196), -h1 (09:42:48.857), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:42:50.459), -/ (09:42:50.549), -h1 (09:42:50.973), -&gt; (09:42:51.209), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -a (09:43:41.313), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:01:09.121), -{ (10:01:29.863), -} (10:01:30.574), -height (10:01:53.339), -: (10:01:53.349), -50px (10:01:53.399), -; (10:01:53.409), -width (10:01:53.719), -: (10:01:53.729), -50px (10:01:53.779), -; (10:01:53.789), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -border (10:08:30.348), -: (10:08:30.358), -1px (10:08:30.398), -solid (10:08:30.458), -gray (10:08:30.508), -; (10:08:30.518), -&lt; (10:13:38.592), -div (10:13:39.615), -&gt; (10:13:40.081), -&lt; (10:13:46.092), -/ (10:13:46.213), -&gt; (10:13:46.973), -. (10:16:02.523), -cell (10:16:03.341), -class (10:16:44.480), -= (10:16:44.581), -" (10:16:44.721), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -= (10:19:00.451), -" (10:19:00.649), -chess (10:19:01.762), -- (10:19:01.973), -board (10:19:03.204), -" (10:19:03.420), -# (10:19:26.647), -chess (10:19:31.372), -- (10:19:31.521), -board (10:19:32.570), -{ (10:19:36.298), -} (10:19:37.045), -width (10:19:39.292), -: (10:19:39.478), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -; (10:25:53.393), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -} (10:39:26.734), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -; (10:39:32.366), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>4.8</v>
       </c>
@@ -2735,12 +2246,11 @@
           <t>-{ (10:01:29.863), -} (10:01:30.574), -height (10:01:53.339), -: (10:01:53.349), -50px (10:01:53.399), -; (10:01:53.409), -width (10:01:53.719), -: (10:01:53.729), -50px (10:01:53.779), -; (10:01:53.789), -border (10:08:30.348), -: (10:08:30.358), -1px (10:08:30.398), -solid (10:08:30.458), -gray (10:08:30.508), -; (10:08:30.518), -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647), -chess (10:19:31.372), -- (10:19:31.521), -board (10:19:32.570), -{ (10:19:36.298), -} (10:19:37.045), -width (10:19:39.292), -: (10:19:39.478), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -border (10:23:53.297), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -; (10:25:53.393), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -} (10:39:26.734), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -: (10:39:30.992), -25px (10:39:32.003), -; (10:39:32.366), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2757,20 +2267,6 @@
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2786,22 +2282,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2822,22 +2302,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2863,22 +2327,11 @@
           <t>⛔</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Scr</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2895,20 +2348,6 @@
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2925,20 +2364,6 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2955,20 +2380,6 @@
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2984,22 +2395,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3021,20 +2416,6 @@
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3082,7 +2463,6 @@
           <t>+doCtyPe (00:00:00), -DOCTYPE (09:34:25.996), +;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -3099,12 +2479,11 @@
           <t>+;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3120,22 +2499,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3156,22 +2519,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3192,22 +2539,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3228,22 +2559,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3296,7 +2611,6 @@
           <t>+/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +0px (00:00:00), +0px (00:00:00), +440px (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +green (00:00:00), +margin (00:00:00), +padding (00:00:00), -! (09:43:41.273), -a (09:43:41.313), -gray (10:08:30.508), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>93.40000000000001</v>
       </c>
@@ -3313,12 +2627,11 @@
           <t>-gray (10:08:30.508) ~0.40, +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), -425px (10:41:03.382) ~0.60, +440px (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +padding (00:00:00), +0px (00:00:00), +; (00:00:00), +: (00:00:00), +green (00:00:00)</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3334,22 +2647,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3370,22 +2667,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3407,20 +2688,6 @@
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3436,22 +2703,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3473,20 +2724,6 @@
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3503,20 +2740,6 @@
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3532,22 +2755,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3568,22 +2775,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3604,22 +2795,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3641,20 +2816,6 @@
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3670,22 +2831,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3738,7 +2883,6 @@
           <t>+- (00:00:00), +2px (00:00:00), +400px (00:00:00), +400px (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +black (00:00:00), +collapse (00:00:00), +collapse (00:00:00), +table (00:00:00), -/ (09:35:09.192), -html (09:35:09.958), -&gt; (09:35:10.226), -&gt; (09:37:18.022), -&lt; (09:37:18.806), -/ (09:37:19.092), -body (09:37:20.214), -&gt; (09:37:20.489), -&lt; (09:42:48.608), -h1 (09:42:48.857), -&gt; (09:42:48.974), -Chess (09:42:49.678), -Board (09:42:50.360), -&lt; (09:42:50.459), -/ (09:42:50.549), -h1 (09:42:50.973), -&lt; (09:43:40.713), -a (09:43:40.723), -href (09:43:40.773), -= (09:43:40.783), -" (09:43:40.793), -https (09:43:40.843), -: (09:43:40.853), -/ (09:43:40.863), -/ (09:43:40.873), -www (09:43:40.903), -. (09:43:40.913), -w3schools (09:43:41.003), -. (09:43:41.013), -com (09:43:41.043), -" (09:43:41.053), -&gt; (09:43:41.063), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -. (09:43:41.233), -com (09:43:41.263), -! (09:43:41.273), -&lt; (09:43:41.293), -/ (09:43:41.303), -a (09:43:41.313), -&gt; (09:43:41.323), -target (09:53:32.699), -= (09:53:32.899), -" (09:53:33.136), -_ (09:53:33.438), -blank (09:53:34.696), -" (09:53:35.083), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -{ (10:01:29.863), -} (10:01:30.574), -: (10:01:53.349), -50px (10:01:53.399), -; (10:01:53.409), -: (10:01:53.729), -50px (10:01:53.779), -; (10:01:53.789), -&lt; (10:03:04.157), -div (10:03:04.187), -&gt; (10:03:04.197), -&lt; (10:03:04.207), -/ (10:03:04.217), -div (10:03:04.247), -&gt; (10:03:04.257), -&lt; (10:03:04.277), -div (10:03:04.307), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -1px (10:08:30.398), -gray (10:08:30.508), -; (10:08:30.518), -div (10:13:39.615), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), -&gt; (10:13:46.973), -. (10:16:02.523), -cell (10:16:03.341), -class (10:16:44.480), -= (10:16:44.581), -cell (10:16:45.428), -" (10:16:45.679), -class (10:17:16.199), -= (10:17:16.209), -" (10:17:16.219), -cell (10:17:16.259), -" (10:17:16.269), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), -id (10:19:00.247), -" (10:19:03.420), -# (10:19:26.647), -} (10:19:37.045), -width (10:19:39.292), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), -&gt; (10:30:44.669), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>4.7</v>
       </c>
@@ -3755,12 +2899,11 @@
           <t>-{ (10:01:29.863), -} (10:01:30.574), -: (10:01:53.349), -50px (10:01:53.399), -; (10:01:53.409), -: (10:01:53.729), -50px (10:01:53.779), -; (10:01:53.789), -1px (10:08:30.398), -gray (10:08:30.508), -; (10:08:30.518), -. (10:16:02.523), -cell (10:16:03.341), -# (10:19:26.647), -} (10:19:37.045), -width (10:19:39.292), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -: (10:23:52.283), -- (10:23:53.510), -box (10:23:53.913), -; (10:23:53.962), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -- (10:25:51.611), -wrap (10:25:52.332), -: (10:25:52.460), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -: (10:28:25.796), -white (10:28:26.840), -; (10:28:27.188), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -background (10:28:44.763), -- (10:28:44.853), -color (10:28:45.540), -: (10:28:45.637), -black (10:28:46.937), -; (10:28:47.044), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003) ~0.40, -425px (10:41:03.382) ~0.60, -; (10:41:03.595), +2px (00:00:00), +black (00:00:00), +; (00:00:00), +- (00:00:00), +collapse (00:00:00), +: (00:00:00), +collapse (00:00:00), +400px (00:00:00), +; (00:00:00), +400px (00:00:00)</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q68" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3776,22 +2919,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3813,20 +2940,6 @@
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3861,7 +2974,6 @@
       <c r="H71" t="n">
         <v>100</v>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
         <v>57.7</v>
       </c>
@@ -3870,7 +2982,6 @@
           <t>+0 (00:00:00), +Chess (00:00:00), +font (00:00:00), +size (00:00:00), +w3schools (00:00:00), -" (09:43:40.793), -" (09:43:41.053), -W3Schools (09:43:41.223), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -chess (10:19:01.762), +;* (10:23:07.806), +400px* (10:23:08.698), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -&lt; (10:30:40.039), -/ (10:30:40.049), -div (10:30:40.079), -&gt; (10:30:40.089), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.199), -= (10:30:40.209), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -&lt; (10:30:40.649), -/ (10:30:40.659), -div (10:30:40.689), -&gt; (10:30:40.699), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.809), -= (10:30:40.819), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -&lt; (10:30:42.479), -/ (10:30:42.489), -div (10:30:42.519), -&gt; (10:30:42.529), -&lt; (10:30:42.549), -div (10:30:42.579), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -&lt; (10:30:43.089), -/ (10:30:43.099), -div (10:30:43.129), -&gt; (10:30:43.139), -&lt; (10:30:43.159), -div (10:30:43.189), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>58.2</v>
       </c>
@@ -3887,12 +2998,11 @@
           <t>+;* (10:23:07.806), +400px* (10:23:08.698), -display (10:25:49.056), -: (10:25:49.159), -flex (10:25:49.961), -; (10:25:50.199), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +font (00:00:00), +size (00:00:00), +0 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3909,20 +3019,6 @@
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3970,7 +3066,6 @@
           <t>+! (00:00:00), +( (00:00:00), +) (00:00:00), +- (00:00:00), +0 (00:00:00), +10px (00:00:00), +10px (00:00:00), +2px (00:00:00), +2px (00:00:00), +50px (00:00:00), +50px (00:00:00), +5px (00:00:00), +5px (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +Inline (00:00:00), +Not (00:00:00), +black (00:00:00), +block (00:00:00), +block (00:00:00), +display (00:00:00), +div (00:00:00), +font (00:00:00), +gray (00:00:00), +height (00:00:00), +inline (00:00:00), +inline (00:00:00), +margin (00:00:00), +padding (00:00:00), +padding (00:00:00), +recommended (00:00:00), +size (00:00:00), +solid (00:00:00), +style (00:00:00), +style (00:00:00), +width (00:00:00), +with (00:00:00), -_ (09:53:33.438), -blank (09:53:34.696), -/ (09:54:45.543), -} (10:01:30.574), -&gt; (10:03:04.257), -&gt; (10:03:04.377), -&gt; (10:03:04.497), -&gt; (10:03:04.617), -&gt; (10:03:04.737), -&gt; (10:03:04.857), -&gt; (10:03:04.977), -1px (10:08:30.398), -&lt; (10:13:46.092), -/ (10:13:46.213), -div (10:13:46.750), +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319), -sizing (10:23:52.062), -- (10:23:53.510), -box (10:23:53.913), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -white (10:28:26.840), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), -light (10:29:10.001), -dark (10:29:13.127), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -div (10:30:31.152), -class (10:30:31.212), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -light (10:30:34.792), -&gt; (10:30:34.872), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -div (10:30:44.659), -&gt; (10:30:44.669), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -offset (10:40:21.332), -left (10:40:38.720), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>20.1</v>
       </c>
@@ -3987,12 +3082,11 @@
           <t>-} (10:01:30.574), -1px (10:08:30.398) ~0.75, +;* (10:23:07.806), +400px* (10:23:08.698), -box (10:23:51.197), -- (10:23:51.319) ~1.00, -sizing (10:23:52.062), -- (10:23:53.510), -box (10:23:53.913), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), -. (10:28:16.770), -light (10:28:17.862), -{ (10:28:18.209), -} (10:28:18.655), -background (10:28:24.658), -- (10:28:24.737), -color (10:28:25.672), -white (10:28:26.840), -. (10:28:28.950), -dark (10:28:29.719), -{ (10:28:30.015), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +; (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00), +2px (00:00:00), +inline (00:00:00), +block (00:00:00)</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q73" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4008,22 +3102,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4076,7 +3154,6 @@
           <t>+10px (00:00:00), +432px (00:00:00), +5px (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +padding (00:00:00), +visit (00:00:00), -Visit (09:43:41.123), -&lt; (09:54:44.535), -div (09:54:45.048), -&gt; (09:54:45.250), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -&gt; (10:03:04.317), -&lt; (10:03:04.327), -/ (10:03:04.337), -div (10:03:04.367), -&gt; (10:03:04.377), -&lt; (10:03:04.397), -div (10:03:04.427), -&gt; (10:03:04.437), -&lt; (10:03:04.447), -/ (10:03:04.457), -div (10:03:04.487), -&gt; (10:03:04.497), -&lt; (10:03:04.517), -div (10:03:04.547), -&gt; (10:03:04.557), -&lt; (10:03:04.567), -/ (10:03:04.577), -div (10:03:04.607), -&gt; (10:03:04.617), -&lt; (10:03:04.637), -div (10:03:04.667), -&gt; (10:03:04.677), -&lt; (10:03:04.687), -/ (10:03:04.697), -div (10:03:04.727), -&gt; (10:03:04.737), -&lt; (10:03:04.757), -div (10:03:04.787), -&gt; (10:03:04.797), -&lt; (10:03:04.807), -/ (10:03:04.817), -div (10:03:04.847), -&gt; (10:03:04.857), -&lt; (10:03:04.877), -div (10:03:04.907), -&gt; (10:03:04.917), -&lt; (10:03:04.927), -/ (10:03:04.937), -div (10:03:04.967), -&gt; (10:03:04.977), -class (10:17:18.773), -= (10:17:18.783), -" (10:17:18.793), -cell (10:17:18.833), -" (10:17:18.843), -class (10:17:20.244), -= (10:17:20.254), -" (10:17:20.264), -cell (10:17:20.304), -" (10:17:20.314), -class (10:17:22.729), -= (10:17:22.739), -" (10:17:22.749), -cell (10:17:22.789), -" (10:17:22.799), -class (10:17:24.201), -= (10:17:24.211), -" (10:17:24.221), -cell (10:17:24.261), -" (10:17:24.271), -class (10:17:26.650), -= (10:17:26.660), -" (10:17:26.670), -cell (10:17:26.710), -" (10:17:26.720), -class (10:17:28.117), -= (10:17:28.127), -" (10:17:28.137), -cell (10:17:28.177), -" (10:17:28.187), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -; (10:28:47.044), -light (10:29:25.682), -dark (10:29:29.356), -light (10:29:34.015), -dark (10:29:37.654), -light (10:29:41.325), -dark (10:29:45.875), -&lt; (10:30:31.122), -div (10:30:31.152), -class (10:30:31.212), -= (10:30:31.222), -" (10:30:31.232), -cell (10:30:31.272), -dark (10:30:31.322), -" (10:30:31.332), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -div (10:30:34.612), -class (10:30:34.672), -= (10:30:34.682), -" (10:30:34.692), -cell (10:30:34.732), -light (10:30:34.792), -" (10:30:34.802), -&gt; (10:30:34.812), -&lt; (10:30:34.822), -/ (10:30:34.832), -div (10:30:34.862), -&gt; (10:30:34.872), -&lt; (10:30:34.892), -div (10:30:34.922), -class (10:30:34.982), -= (10:30:34.992), -" (10:30:35.002), -cell (10:30:35.042), -dark (10:30:35.092), -" (10:30:35.102), -&gt; (10:30:35.112), -&lt; (10:30:35.122), -/ (10:30:35.132), -div (10:30:35.162), -&gt; (10:30:35.172), -&lt; (10:30:35.192), -div (10:30:35.222), -class (10:30:35.282), -= (10:30:35.292), -" (10:30:35.302), -cell (10:30:35.342), -light (10:30:35.402), -" (10:30:35.412), -&gt; (10:30:35.422), -&lt; (10:30:35.432), -/ (10:30:35.442), -div (10:30:35.472), -&gt; (10:30:35.482), -&lt; (10:30:35.502), -div (10:30:35.532), -class (10:30:35.592), -= (10:30:35.602), -" (10:30:35.612), -cell (10:30:35.652), -dark (10:30:35.702), -" (10:30:35.712), -&gt; (10:30:35.722), -&lt; (10:30:35.732), -/ (10:30:35.742), -div (10:30:35.772), -&gt; (10:30:35.782), -&lt; (10:30:35.802), -div (10:30:35.832), -class (10:30:35.892), -= (10:30:35.902), -" (10:30:35.912), -cell (10:30:35.952), -light (10:30:36.012), -" (10:30:36.022), -&gt; (10:30:36.032), -&lt; (10:30:36.042), -/ (10:30:36.052), -div (10:30:36.082), -&gt; (10:30:36.092), -&lt; (10:30:36.112), -div (10:30:36.142), -class (10:30:36.202), -= (10:30:36.212), -" (10:30:36.222), -cell (10:30:36.262), -dark (10:30:36.312), -" (10:30:36.322), -&gt; (10:30:36.332), -&lt; (10:30:36.342), -/ (10:30:36.352), -div (10:30:36.382), -&gt; (10:30:36.392), -&lt; (10:30:36.412), -div (10:30:36.442), -class (10:30:36.502), -= (10:30:36.512), -" (10:30:36.522), -cell (10:30:36.562), -light (10:30:36.622), -" (10:30:36.632), -&gt; (10:30:36.642), -&lt; (10:30:36.652), -/ (10:30:36.662), -div (10:30:36.692), -&gt; (10:30:36.702), -&lt; (10:30:38.682), -div (10:30:38.712), -class (10:30:38.772), -= (10:30:38.782), -" (10:30:38.792), -cell (10:30:38.832), -light (10:30:38.892), -" (10:30:38.902), -&gt; (10:30:38.912), -&lt; (10:30:38.922), -/ (10:30:38.932), -div (10:30:38.962), -&gt; (10:30:38.972), -&lt; (10:30:38.992), -div (10:30:39.022), -class (10:30:39.082), -= (10:30:39.092), -" (10:30:39.102), -cell (10:30:39.142), -&lt; (10:30:39.143), -div (10:30:39.173), -dark (10:30:39.192), -" (10:30:39.202), -&gt; (10:30:39.212), -&lt; (10:30:39.222), -/ (10:30:39.232), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -div (10:30:39.262), -&gt; (10:30:39.272), -&lt; (10:30:39.292), -cell (10:30:39.293), -div (10:30:39.322), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -class (10:30:39.382), -&lt; (10:30:39.383), -= (10:30:39.392), -/ (10:30:39.393), -" (10:30:39.402), -div (10:30:39.423), -&gt; (10:30:39.433), -cell (10:30:39.442), -&lt; (10:30:39.453), -div (10:30:39.483), -light (10:30:39.502), -" (10:30:39.512), -&gt; (10:30:39.522), -&lt; (10:30:39.532), -/ (10:30:39.542), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -div (10:30:39.572), -&gt; (10:30:39.582), -&lt; (10:30:39.602), -cell (10:30:39.603), -div (10:30:39.632), -dark (10:30:39.653), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.683), -class (10:30:39.692), -/ (10:30:39.693), -= (10:30:39.702), -" (10:30:39.712), -div (10:30:39.723), -&gt; (10:30:39.733), -cell (10:30:39.752), -&lt; (10:30:39.753), -div (10:30:39.783), -&lt; (10:30:39.799), -dark (10:30:39.802), -" (10:30:39.812), -&gt; (10:30:39.822), -div (10:30:39.829), -&lt; (10:30:39.832), -/ (10:30:39.842), -class (10:30:39.843), -= (10:30:39.853), -" (10:30:39.863), -div (10:30:39.872), -&gt; (10:30:39.882), -class (10:30:39.889), -= (10:30:39.899), -&lt; (10:30:39.902), -cell (10:30:39.903), -" (10:30:39.909), -div (10:30:39.932), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -class (10:30:39.992), -&lt; (10:30:39.993), -= (10:30:40.002), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.012), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -cell (10:30:40.052), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -light (10:30:40.112), -" (10:30:40.122), -&gt; (10:30:40.132), -div (10:30:40.139), -&lt; (10:30:40.142), -/ (10:30:40.152), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -div (10:30:40.182), -&gt; (10:30:40.192), -class (10:30:40.199), -= (10:30:40.209), -&lt; (10:30:40.212), -cell (10:30:40.213), -" (10:30:40.219), -div (10:30:40.242), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -&lt; (10:30:40.293), -class (10:30:40.302), -/ (10:30:40.303), -dark (10:30:40.309), -= (10:30:40.312), -" (10:30:40.319), -" (10:30:40.322), -&gt; (10:30:40.329), -div (10:30:40.333), -&lt; (10:30:40.339), -&gt; (10:30:40.343), -/ (10:30:40.349), -cell (10:30:40.362), -&lt; (10:30:40.363), -div (10:30:40.379), -&gt; (10:30:40.389), -div (10:30:40.393), -&lt; (10:30:40.409), -dark (10:30:40.412), -" (10:30:40.422), -&gt; (10:30:40.432), -div (10:30:40.439), -&lt; (10:30:40.442), -/ (10:30:40.452), -class (10:30:40.453), -= (10:30:40.463), -" (10:30:40.473), -div (10:30:40.482), -&gt; (10:30:40.492), -class (10:30:40.499), -= (10:30:40.509), -&lt; (10:30:40.512), -cell (10:30:40.513), -" (10:30:40.519), -div (10:30:40.542), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -class (10:30:40.602), -&lt; (10:30:40.603), -= (10:30:40.612), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.622), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -cell (10:30:40.662), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -light (10:30:40.722), -" (10:30:40.732), -&gt; (10:30:40.742), -div (10:30:40.749), -&lt; (10:30:40.752), -/ (10:30:40.762), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -div (10:30:40.792), -&gt; (10:30:40.802), -class (10:30:40.809), -= (10:30:40.819), -&lt; (10:30:40.822), -cell (10:30:40.823), -" (10:30:40.829), -div (10:30:40.852), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -&lt; (10:30:40.903), -class (10:30:40.912), -/ (10:30:40.913), -dark (10:30:40.919), -= (10:30:40.922), -" (10:30:40.929), -" (10:30:40.932), -&gt; (10:30:40.939), -div (10:30:40.943), -&lt; (10:30:40.949), -&gt; (10:30:40.953), -/ (10:30:40.959), -cell (10:30:40.972), -&lt; (10:30:40.973), -div (10:30:40.989), -&gt; (10:30:40.999), -div (10:30:41.003), -&lt; (10:30:41.019), -dark (10:30:41.022), -" (10:30:41.032), -&gt; (10:30:41.042), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -class (10:30:41.063), -= (10:30:41.073), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -" (10:30:41.542), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -cell (10:30:41.582), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -light (10:30:41.642), -" (10:30:41.652), -div (10:30:41.659), -&gt; (10:30:41.662), -&lt; (10:30:41.672), -/ (10:30:41.682), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -div (10:30:41.712), -class (10:30:41.719), -&gt; (10:30:41.722), -= (10:30:41.729), -" (10:30:41.739), -&lt; (10:30:41.742), -cell (10:30:41.743), -div (10:30:41.772), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -class (10:30:41.832), -/ (10:30:41.833), -light (10:30:41.839), -= (10:30:41.842), -" (10:30:41.849), -" (10:30:41.852), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -cell (10:30:41.892), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -dark (10:30:41.942), -" (10:30:41.952), -&gt; (10:30:41.962), -div (10:30:41.969), -&lt; (10:30:41.972), -/ (10:30:41.982), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -div (10:30:42.012), -&gt; (10:30:42.022), -class (10:30:42.029), -= (10:30:42.039), -&lt; (10:30:42.042), -cell (10:30:42.043), -" (10:30:42.049), -div (10:30:42.072), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -class (10:30:42.132), -&lt; (10:30:42.133), -dark (10:30:42.139), -= (10:30:42.142), -/ (10:30:42.143), -" (10:30:42.149), -" (10:30:42.152), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -cell (10:30:42.192), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -light (10:30:42.252), -" (10:30:42.262), -&gt; (10:30:42.272), -div (10:30:42.279), -&lt; (10:30:42.282), -/ (10:30:42.292), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -div (10:30:42.322), -&gt; (10:30:42.332), -class (10:30:42.339), -= (10:30:42.349), -&lt; (10:30:42.352), -cell (10:30:42.353), -" (10:30:42.359), -div (10:30:42.382), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -class (10:30:42.442), -/ (10:30:42.443), -dark (10:30:42.449), -= (10:30:42.452), -" (10:30:42.459), -" (10:30:42.462), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -cell (10:30:42.502), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -dark (10:30:42.552), -" (10:30:42.562), -&gt; (10:30:42.572), -div (10:30:42.579), -&lt; (10:30:42.582), -/ (10:30:42.592), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -div (10:30:42.622), -&gt; (10:30:42.632), -class (10:30:42.639), -= (10:30:42.649), -&lt; (10:30:42.652), -cell (10:30:42.653), -" (10:30:42.659), -div (10:30:42.682), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -class (10:30:42.742), -&lt; (10:30:42.743), -= (10:30:42.752), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.762), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -cell (10:30:42.802), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -light (10:30:42.862), -" (10:30:42.872), -&gt; (10:30:42.882), -div (10:30:42.889), -&lt; (10:30:42.892), -/ (10:30:42.902), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -div (10:30:42.932), -&gt; (10:30:42.942), -class (10:30:42.949), -= (10:30:42.959), -&lt; (10:30:42.962), -cell (10:30:42.963), -" (10:30:42.969), -div (10:30:42.992), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -class (10:30:43.052), -/ (10:30:43.053), -dark (10:30:43.059), -= (10:30:43.062), -" (10:30:43.069), -" (10:30:43.072), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -cell (10:30:43.112), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -dark (10:30:43.162), -" (10:30:43.172), -&gt; (10:30:43.182), -div (10:30:43.189), -&lt; (10:30:43.192), -/ (10:30:43.202), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -div (10:30:43.232), -&gt; (10:30:43.242), -class (10:30:43.249), -= (10:30:43.259), -&lt; (10:30:43.262), -cell (10:30:43.263), -" (10:30:43.269), -div (10:30:43.292), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -class (10:30:43.352), -&lt; (10:30:43.353), -= (10:30:43.362), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -&gt; (10:30:43.552), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), -" (10:30:44.489), -cell (10:30:44.529), -light (10:30:44.589), -" (10:30:44.599), -&gt; (10:30:44.609), -&lt; (10:30:44.619), -/ (10:30:44.629), -div (10:30:44.659), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
         <v>12.4</v>
       </c>
@@ -4093,12 +3170,11 @@
           <t>+display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382) ~0.60, +432px (00:00:00), +; (00:00:00), +10px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +5px (00:00:00)</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q75" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4114,22 +3190,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4150,22 +3210,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4218,7 +3262,6 @@
           <t>+- (00:00:00), +0 (00:00:00), +2px (00:00:00), +50px (00:00:00), +50px (00:00:00), +: (00:00:00), +background (00:00:00), +black (00:00:00), +board (00:00:00), +chess (00:00:00), +color (00:00:00), +font (00:00:00), +height (00:00:00), +size (00:00:00), +style (00:00:00), +visit (00:00:00), +w3schools (00:00:00), +width (00:00:00), -Chess (09:42:49.678), -Board (09:42:50.360), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -&lt; (09:54:45.396), -/ (09:54:45.543), -div (09:54:46.214), -&gt; (09:54:46.231), -1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), -display (10:25:49.056), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -light (10:29:10.001), -div (10:30:31.152), -class (10:30:31.212), -cell (10:30:31.272), -dark (10:30:31.322), -&gt; (10:30:31.342), -&lt; (10:30:31.352), -/ (10:30:31.362), -div (10:30:31.392), -&gt; (10:30:31.402), -&lt; (10:30:34.582), -class (10:30:34.672), -= (10:30:34.682), -&lt; (10:30:36.652), -div (10:30:36.692), -class (10:30:38.772), -= (10:30:38.782), -&lt; (10:30:39.143), -div (10:30:39.173), -class (10:30:39.233), -= (10:30:39.243), -" (10:30:39.253), -cell (10:30:39.293), -light (10:30:39.353), -" (10:30:39.363), -&gt; (10:30:39.373), -&lt; (10:30:39.383), -/ (10:30:39.393), -div (10:30:39.423), -&gt; (10:30:39.433), -&lt; (10:30:39.453), -div (10:30:39.483), -class (10:30:39.543), -= (10:30:39.553), -" (10:30:39.563), -cell (10:30:39.603), -" (10:30:39.663), -&gt; (10:30:39.673), -&lt; (10:30:39.799), -div (10:30:39.829), -" (10:30:39.863), -class (10:30:39.889), -= (10:30:39.899), -cell (10:30:39.903), -" (10:30:39.909), -cell (10:30:39.949), -light (10:30:39.963), -" (10:30:39.973), -&gt; (10:30:39.983), -&lt; (10:30:39.993), -/ (10:30:40.003), -light (10:30:40.009), -" (10:30:40.019), -&gt; (10:30:40.029), -div (10:30:40.033), -&lt; (10:30:40.039), -&gt; (10:30:40.043), -/ (10:30:40.049), -&lt; (10:30:40.063), -div (10:30:40.079), -&gt; (10:30:40.089), -div (10:30:40.093), -&lt; (10:30:40.109), -div (10:30:40.139), -class (10:30:40.153), -= (10:30:40.163), -" (10:30:40.173), -class (10:30:40.199), -= (10:30:40.209), -cell (10:30:40.213), -" (10:30:40.219), -cell (10:30:40.259), -dark (10:30:40.263), -" (10:30:40.273), -&gt; (10:30:40.283), -dark (10:30:40.309), -" (10:30:40.319), -&gt; (10:30:40.329), -&lt; (10:30:40.339), -/ (10:30:40.349), -div (10:30:40.379), -&gt; (10:30:40.389), -&lt; (10:30:40.409), -div (10:30:40.439), -" (10:30:40.473), -class (10:30:40.499), -= (10:30:40.509), -cell (10:30:40.513), -" (10:30:40.519), -cell (10:30:40.559), -light (10:30:40.573), -" (10:30:40.583), -&gt; (10:30:40.593), -&lt; (10:30:40.603), -/ (10:30:40.613), -light (10:30:40.619), -" (10:30:40.629), -&gt; (10:30:40.639), -div (10:30:40.643), -&lt; (10:30:40.649), -&gt; (10:30:40.653), -/ (10:30:40.659), -&lt; (10:30:40.673), -div (10:30:40.689), -&gt; (10:30:40.699), -div (10:30:40.703), -&lt; (10:30:40.719), -div (10:30:40.749), -class (10:30:40.763), -= (10:30:40.773), -" (10:30:40.783), -class (10:30:40.809), -= (10:30:40.819), -cell (10:30:40.823), -" (10:30:40.829), -cell (10:30:40.869), -dark (10:30:40.873), -" (10:30:40.883), -&gt; (10:30:40.893), -dark (10:30:40.919), -" (10:30:40.929), -&gt; (10:30:40.939), -&lt; (10:30:40.949), -/ (10:30:40.959), -div (10:30:40.989), -&gt; (10:30:40.999), -&lt; (10:30:41.019), -div (10:30:41.049), -&lt; (10:30:41.052), -/ (10:30:41.062), -" (10:30:41.083), -div (10:30:41.092), -&gt; (10:30:41.102), -class (10:30:41.109), -= (10:30:41.119), -cell (10:30:41.123), -" (10:30:41.129), -&lt; (10:30:41.132), -div (10:30:41.162), -cell (10:30:41.169), -light (10:30:41.183), -" (10:30:41.193), -&gt; (10:30:41.203), -&lt; (10:30:41.213), -class (10:30:41.222), -/ (10:30:41.223), -light (10:30:41.229), -= (10:30:41.232), -" (10:30:41.239), -" (10:30:41.242), -&gt; (10:30:41.249), -div (10:30:41.253), -&lt; (10:30:41.259), -&gt; (10:30:41.263), -/ (10:30:41.269), -cell (10:30:41.282), -&lt; (10:30:41.283), -div (10:30:41.299), -&gt; (10:30:41.309), -div (10:30:41.313), -&lt; (10:30:41.329), -dark (10:30:41.332), -" (10:30:41.342), -&gt; (10:30:41.352), -div (10:30:41.359), -&lt; (10:30:41.362), -/ (10:30:41.372), -class (10:30:41.373), -= (10:30:41.383), -" (10:30:41.393), -div (10:30:41.402), -&gt; (10:30:41.412), -class (10:30:41.419), -= (10:30:41.429), -&lt; (10:30:41.432), -cell (10:30:41.433), -" (10:30:41.439), -div (10:30:41.462), -cell (10:30:41.479), -dark (10:30:41.483), -" (10:30:41.493), -&gt; (10:30:41.503), -&lt; (10:30:41.513), -class (10:30:41.522), -/ (10:30:41.523), -dark (10:30:41.529), -= (10:30:41.532), -" (10:30:41.539), -&gt; (10:30:41.549), -div (10:30:41.553), -&lt; (10:30:41.559), -&gt; (10:30:41.563), -/ (10:30:41.569), -&lt; (10:30:41.593), -div (10:30:41.599), -&gt; (10:30:41.609), -div (10:30:41.623), -&lt; (10:30:41.629), -div (10:30:41.659), -class (10:30:41.683), -= (10:30:41.693), -" (10:30:41.703), -class (10:30:41.719), -= (10:30:41.729), -" (10:30:41.739), -cell (10:30:41.743), -cell (10:30:41.779), -dark (10:30:41.793), -" (10:30:41.803), -&gt; (10:30:41.813), -&lt; (10:30:41.823), -/ (10:30:41.833), -light (10:30:41.839), -" (10:30:41.849), -&gt; (10:30:41.859), -div (10:30:41.863), -&lt; (10:30:41.869), -&gt; (10:30:41.873), -/ (10:30:41.879), -&lt; (10:30:41.893), -div (10:30:41.909), -&gt; (10:30:41.919), -div (10:30:41.923), -&lt; (10:30:41.939), -div (10:30:41.969), -class (10:30:41.983), -= (10:30:41.993), -" (10:30:42.003), -class (10:30:42.029), -= (10:30:42.039), -cell (10:30:42.043), -" (10:30:42.049), -cell (10:30:42.089), -light (10:30:42.103), -" (10:30:42.113), -&gt; (10:30:42.123), -&lt; (10:30:42.133), -dark (10:30:42.139), -/ (10:30:42.143), -" (10:30:42.149), -&gt; (10:30:42.159), -&lt; (10:30:42.169), -div (10:30:42.173), -/ (10:30:42.179), -&gt; (10:30:42.183), -&lt; (10:30:42.203), -div (10:30:42.209), -&gt; (10:30:42.219), -div (10:30:42.233), -&lt; (10:30:42.249), -div (10:30:42.279), -class (10:30:42.293), -= (10:30:42.303), -" (10:30:42.313), -class (10:30:42.339), -= (10:30:42.349), -cell (10:30:42.353), -" (10:30:42.359), -cell (10:30:42.399), -dark (10:30:42.403), -" (10:30:42.413), -&gt; (10:30:42.423), -&lt; (10:30:42.433), -/ (10:30:42.443), -dark (10:30:42.449), -" (10:30:42.459), -&gt; (10:30:42.469), -div (10:30:42.473), -&lt; (10:30:42.479), -&gt; (10:30:42.483), -/ (10:30:42.489), -&lt; (10:30:42.503), -div (10:30:42.519), -&gt; (10:30:42.529), -div (10:30:42.533), -&lt; (10:30:42.549), -div (10:30:42.579), -class (10:30:42.593), -= (10:30:42.603), -" (10:30:42.613), -class (10:30:42.639), -= (10:30:42.649), -cell (10:30:42.653), -" (10:30:42.659), -cell (10:30:42.699), -light (10:30:42.713), -" (10:30:42.723), -&gt; (10:30:42.733), -&lt; (10:30:42.743), -/ (10:30:42.753), -light (10:30:42.759), -" (10:30:42.769), -&gt; (10:30:42.779), -div (10:30:42.783), -&lt; (10:30:42.789), -&gt; (10:30:42.793), -/ (10:30:42.799), -&lt; (10:30:42.813), -div (10:30:42.829), -&gt; (10:30:42.839), -div (10:30:42.843), -&lt; (10:30:42.859), -div (10:30:42.889), -class (10:30:42.903), -= (10:30:42.913), -" (10:30:42.923), -class (10:30:42.949), -= (10:30:42.959), -cell (10:30:42.963), -" (10:30:42.969), -cell (10:30:43.009), -dark (10:30:43.013), -" (10:30:43.023), -&gt; (10:30:43.033), -&lt; (10:30:43.043), -/ (10:30:43.053), -dark (10:30:43.059), -" (10:30:43.069), -&gt; (10:30:43.079), -div (10:30:43.083), -&lt; (10:30:43.089), -&gt; (10:30:43.093), -/ (10:30:43.099), -&lt; (10:30:43.113), -div (10:30:43.129), -&gt; (10:30:43.139), -div (10:30:43.143), -&lt; (10:30:43.159), -div (10:30:43.189), -class (10:30:43.203), -= (10:30:43.213), -" (10:30:43.223), -class (10:30:43.249), -= (10:30:43.259), -cell (10:30:43.263), -" (10:30:43.269), -cell (10:30:43.309), -light (10:30:43.323), -" (10:30:43.333), -&gt; (10:30:43.343), -&lt; (10:30:43.353), -/ (10:30:43.363), -light (10:30:43.369), -" (10:30:43.372), -" (10:30:43.379), -&gt; (10:30:43.389), -div (10:30:43.393), -&lt; (10:30:43.399), -&gt; (10:30:43.403), -/ (10:30:43.409), -cell (10:30:43.412), -&lt; (10:30:43.423), -div (10:30:43.439), -&gt; (10:30:43.449), -div (10:30:43.453), -&lt; (10:30:43.469), -light (10:30:43.472), -" (10:30:43.482), -&gt; (10:30:43.492), -div (10:30:43.499), -&lt; (10:30:43.502), -/ (10:30:43.512), -class (10:30:43.513), -= (10:30:43.523), -" (10:30:43.533), -div (10:30:43.542), -class (10:30:43.559), -= (10:30:43.569), -cell (10:30:43.573), -" (10:30:43.579), -cell (10:30:43.619), -dark (10:30:43.623), -" (10:30:43.633), -&gt; (10:30:43.643), -&lt; (10:30:43.653), -/ (10:30:43.663), -dark (10:30:43.669), -" (10:30:43.679), -&gt; (10:30:43.689), -div (10:30:43.693), -&lt; (10:30:43.699), -&gt; (10:30:43.703), -/ (10:30:43.709), -&lt; (10:30:43.723), -div (10:30:43.739), -&gt; (10:30:43.749), -div (10:30:43.753), -&lt; (10:30:43.769), -div (10:30:43.799), -class (10:30:43.813), -= (10:30:43.823), -" (10:30:43.833), -class (10:30:43.859), -= (10:30:43.869), -cell (10:30:43.873), -" (10:30:43.879), -cell (10:30:43.919), -light (10:30:43.933), -" (10:30:43.943), -&gt; (10:30:43.953), -&lt; (10:30:43.963), -/ (10:30:43.973), -light (10:30:43.979), -" (10:30:43.989), -&gt; (10:30:43.999), -div (10:30:44.003), -&lt; (10:30:44.009), -&gt; (10:30:44.013), -/ (10:30:44.019), -div (10:30:44.049), -&gt; (10:30:44.059), -&lt; (10:30:44.079), -div (10:30:44.109), -class (10:30:44.169), -= (10:30:44.179), -" (10:30:44.189), -cell (10:30:44.229), -dark (10:30:44.279), -" (10:30:44.289), -&gt; (10:30:44.299), -&lt; (10:30:44.309), -/ (10:30:44.319), -div (10:30:44.349), -&gt; (10:30:44.359), -&lt; (10:30:44.379), -div (10:30:44.409), -class (10:30:44.469), -= (10:30:44.479), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
         <v>51.3</v>
       </c>
@@ -4235,12 +3278,11 @@
           <t>-1px (10:08:30.398) ~0.67, +;* (10:23:07.806), +400px* (10:23:08.698), -display (10:25:49.056), -flex (10:25:49.961), -flex (10:25:51.452), -wrap (10:25:52.332), -wrap (10:25:53.144), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), +font (00:00:00), +size (00:00:00), +0 (00:00:00), +2px (00:00:00)</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q78" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4288,11 +3330,9 @@
           <t>+432px (00:00:00), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>100</v>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>91</v>
       </c>
@@ -4301,12 +3341,11 @@
           <t>+background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -425px (10:41:03.382) ~0.60, +432px (00:00:00)</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4322,22 +3361,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4390,7 +3413,6 @@
           <t>+W3schools (00:00:00), -W3Schools (09:43:41.223), +400px* (10:23:08.698), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -4407,12 +3429,11 @@
           <t>+400px* (10:23:08.698), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q81" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4459,7 +3480,6 @@
           <t>+= (00:00:00), +color (00:00:00), +red (00:00:00), +style (00:00:00), +400px* (10:23:08.698), -} (10:28:30.345), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>98.3</v>
       </c>
@@ -4476,12 +3496,11 @@
           <t>+400px* (10:23:08.698), -} (10:28:30.345), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382)</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4529,7 +3548,6 @@
           <t>+2px (00:00:00), +visit (00:00:00), +w3schools (00:00:00), -Visit (09:43:41.123), -W3Schools (09:43:41.223), -1px (10:08:30.398), +;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -left (10:40:20.194), -- (10:40:20.358), -offset (10:40:21.332), -left (10:40:38.720), -- (10:40:38.730), -offset (10:40:38.790), -left (10:40:42.564), -- (10:40:42.574), -offset (10:40:42.634), -left (10:40:46.355), -- (10:40:46.365), -offset (10:40:46.425), -425px (10:41:03.382), -; (10:41:03.595)</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>98.5</v>
       </c>
@@ -4546,12 +3564,11 @@
           <t>-1px (10:08:30.398) ~0.67, +;* (10:23:07.806), +400px* (10:23:08.698), +font* (10:26:42.250), +-* (10:26:42.251), +size* (10:26:42.255), +:* (10:26:42.256), +0* (10:26:42.258), +;* (10:26:42.259), +display* (10:26:45.844), +:* (10:26:45.845), +inline* (10:26:45.852), +-* (10:26:45.853), +block* (10:26:45.858), +;* (10:26:45.859), -} (10:28:30.345), -: (10:28:45.637), -; (10:28:47.044), +background* (10:36:49.964), +-* (10:36:49.965), +color* (10:36:49.970), +:* (10:36:49.971), +black* (10:36:49.977), +;* (10:36:49.978), -. (10:39:22.910), -left (10:39:23.738), -- (10:39:23.809), -offset (10:39:25.121), -{ (10:39:26.086), -margin (10:39:29.939), -- (10:39:30.002), -left (10:39:30.891), -25px (10:39:32.003), -425px (10:41:03.382), -; (10:41:03.595), +2px (00:00:00)</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4567,22 +3584,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4603,22 +3604,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4640,20 +3625,6 @@
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
       <c r="T86" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4675,20 +3646,6 @@
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
       <c r="T87" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4710,20 +3667,6 @@
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
       <c r="T88" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4745,20 +3688,6 @@
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
       <c r="T89" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4780,20 +3709,6 @@
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
       <c r="T90" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4815,20 +3730,6 @@
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
       <c r="T91" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4850,20 +3751,6 @@
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
       <c r="T92" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4885,20 +3772,6 @@
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
       <c r="T93" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4920,20 +3793,6 @@
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
       <c r="T94" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4955,20 +3814,6 @@
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
       <c r="T95" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -4990,20 +3835,6 @@
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
       <c r="T96" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5025,20 +3856,6 @@
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5060,20 +3877,6 @@
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
       <c r="T98" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5095,20 +3898,6 @@
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5130,20 +3919,6 @@
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
       <c r="T100" t="inlineStr">
         <is>
           <t>LLM</t>
